--- a/outputs/svm/rip_temperatura.xlsx
+++ b/outputs/svm/rip_temperatura.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/u0186653/Desktop/research/dingen/deepnir/outputs/svm/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC548165-4642-1B45-BCEF-A1B53221CBE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D972551-3636-E84B-983D-8AE8263A473F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="21680" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="432" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="384" uniqueCount="22">
   <si>
     <t>Crop</t>
   </si>
@@ -331,13 +331,46 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
@@ -349,41 +382,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -728,10 +728,10 @@
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A2" s="4" t="s">
+      <c r="A2" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="17" t="s">
         <v>9</v>
       </c>
       <c r="C2" t="s">
@@ -742,8 +742,8 @@
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A3" s="6"/>
-      <c r="B3" s="7"/>
+      <c r="A3" s="15"/>
+      <c r="B3" s="18"/>
       <c r="C3" t="s">
         <v>18</v>
       </c>
@@ -752,8 +752,8 @@
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A4" s="6"/>
-      <c r="B4" s="7"/>
+      <c r="A4" s="15"/>
+      <c r="B4" s="18"/>
       <c r="C4" t="s">
         <v>19</v>
       </c>
@@ -762,8 +762,8 @@
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A5" s="6"/>
-      <c r="B5" s="8"/>
+      <c r="A5" s="15"/>
+      <c r="B5" s="19"/>
       <c r="C5" t="s">
         <v>20</v>
       </c>
@@ -772,8 +772,8 @@
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A6" s="6"/>
-      <c r="B6" s="9" t="s">
+      <c r="A6" s="15"/>
+      <c r="B6" s="20" t="s">
         <v>10</v>
       </c>
       <c r="C6" t="s">
@@ -784,8 +784,8 @@
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A7" s="6"/>
-      <c r="B7" s="7"/>
+      <c r="A7" s="15"/>
+      <c r="B7" s="18"/>
       <c r="C7" t="s">
         <v>18</v>
       </c>
@@ -794,8 +794,8 @@
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A8" s="6"/>
-      <c r="B8" s="7"/>
+      <c r="A8" s="15"/>
+      <c r="B8" s="18"/>
       <c r="C8" t="s">
         <v>19</v>
       </c>
@@ -804,8 +804,8 @@
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A9" s="6"/>
-      <c r="B9" s="8"/>
+      <c r="A9" s="15"/>
+      <c r="B9" s="19"/>
       <c r="C9" t="s">
         <v>20</v>
       </c>
@@ -814,8 +814,8 @@
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A10" s="6"/>
-      <c r="B10" s="9" t="s">
+      <c r="A10" s="15"/>
+      <c r="B10" s="20" t="s">
         <v>11</v>
       </c>
       <c r="C10" t="s">
@@ -826,8 +826,8 @@
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A11" s="6"/>
-      <c r="B11" s="7"/>
+      <c r="A11" s="15"/>
+      <c r="B11" s="18"/>
       <c r="C11" t="s">
         <v>18</v>
       </c>
@@ -836,8 +836,8 @@
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A12" s="6"/>
-      <c r="B12" s="7"/>
+      <c r="A12" s="15"/>
+      <c r="B12" s="18"/>
       <c r="C12" t="s">
         <v>19</v>
       </c>
@@ -846,8 +846,8 @@
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A13" s="6"/>
-      <c r="B13" s="8"/>
+      <c r="A13" s="15"/>
+      <c r="B13" s="19"/>
       <c r="C13" t="s">
         <v>20</v>
       </c>
@@ -856,8 +856,8 @@
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A14" s="6"/>
-      <c r="B14" s="9" t="s">
+      <c r="A14" s="15"/>
+      <c r="B14" s="20" t="s">
         <v>12</v>
       </c>
       <c r="C14" t="s">
@@ -868,8 +868,8 @@
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A15" s="6"/>
-      <c r="B15" s="7"/>
+      <c r="A15" s="15"/>
+      <c r="B15" s="18"/>
       <c r="C15" t="s">
         <v>18</v>
       </c>
@@ -878,8 +878,8 @@
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A16" s="6"/>
-      <c r="B16" s="7"/>
+      <c r="A16" s="15"/>
+      <c r="B16" s="18"/>
       <c r="C16" t="s">
         <v>19</v>
       </c>
@@ -888,8 +888,8 @@
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A17" s="6"/>
-      <c r="B17" s="8"/>
+      <c r="A17" s="15"/>
+      <c r="B17" s="19"/>
       <c r="C17" t="s">
         <v>20</v>
       </c>
@@ -898,8 +898,8 @@
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A18" s="6"/>
-      <c r="B18" s="9" t="s">
+      <c r="A18" s="15"/>
+      <c r="B18" s="20" t="s">
         <v>13</v>
       </c>
       <c r="C18" t="s">
@@ -910,8 +910,8 @@
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A19" s="6"/>
-      <c r="B19" s="7"/>
+      <c r="A19" s="15"/>
+      <c r="B19" s="18"/>
       <c r="C19" t="s">
         <v>18</v>
       </c>
@@ -920,8 +920,8 @@
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A20" s="6"/>
-      <c r="B20" s="7"/>
+      <c r="A20" s="15"/>
+      <c r="B20" s="18"/>
       <c r="C20" t="s">
         <v>19</v>
       </c>
@@ -930,8 +930,8 @@
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A21" s="6"/>
-      <c r="B21" s="8"/>
+      <c r="A21" s="15"/>
+      <c r="B21" s="19"/>
       <c r="C21" t="s">
         <v>20</v>
       </c>
@@ -940,8 +940,8 @@
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A22" s="6"/>
-      <c r="B22" s="9" t="s">
+      <c r="A22" s="15"/>
+      <c r="B22" s="20" t="s">
         <v>14</v>
       </c>
       <c r="C22" t="s">
@@ -952,8 +952,8 @@
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A23" s="6"/>
-      <c r="B23" s="7"/>
+      <c r="A23" s="15"/>
+      <c r="B23" s="18"/>
       <c r="C23" t="s">
         <v>18</v>
       </c>
@@ -962,8 +962,8 @@
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A24" s="6"/>
-      <c r="B24" s="7"/>
+      <c r="A24" s="15"/>
+      <c r="B24" s="18"/>
       <c r="C24" t="s">
         <v>19</v>
       </c>
@@ -972,8 +972,8 @@
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A25" s="6"/>
-      <c r="B25" s="8"/>
+      <c r="A25" s="15"/>
+      <c r="B25" s="19"/>
       <c r="C25" t="s">
         <v>20</v>
       </c>
@@ -982,8 +982,8 @@
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A26" s="6"/>
-      <c r="B26" s="9" t="s">
+      <c r="A26" s="15"/>
+      <c r="B26" s="20" t="s">
         <v>15</v>
       </c>
       <c r="C26" t="s">
@@ -994,8 +994,8 @@
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A27" s="6"/>
-      <c r="B27" s="7"/>
+      <c r="A27" s="15"/>
+      <c r="B27" s="18"/>
       <c r="C27" t="s">
         <v>18</v>
       </c>
@@ -1004,8 +1004,8 @@
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A28" s="6"/>
-      <c r="B28" s="7"/>
+      <c r="A28" s="15"/>
+      <c r="B28" s="18"/>
       <c r="C28" t="s">
         <v>19</v>
       </c>
@@ -1014,8 +1014,8 @@
       </c>
     </row>
     <row r="29" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="10"/>
-      <c r="B29" s="11"/>
+      <c r="A29" s="16"/>
+      <c r="B29" s="21"/>
       <c r="C29" t="s">
         <v>20</v>
       </c>
@@ -1024,10 +1024,10 @@
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A30" s="4" t="s">
+      <c r="A30" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="B30" s="5" t="s">
+      <c r="B30" s="17" t="s">
         <v>16</v>
       </c>
       <c r="C30" t="s">
@@ -1038,8 +1038,8 @@
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A31" s="6"/>
-      <c r="B31" s="7"/>
+      <c r="A31" s="15"/>
+      <c r="B31" s="18"/>
       <c r="C31" t="s">
         <v>18</v>
       </c>
@@ -1048,8 +1048,8 @@
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A32" s="6"/>
-      <c r="B32" s="7"/>
+      <c r="A32" s="15"/>
+      <c r="B32" s="18"/>
       <c r="C32" t="s">
         <v>19</v>
       </c>
@@ -1058,8 +1058,8 @@
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A33" s="6"/>
-      <c r="B33" s="8"/>
+      <c r="A33" s="15"/>
+      <c r="B33" s="19"/>
       <c r="C33" t="s">
         <v>20</v>
       </c>
@@ -1068,8 +1068,8 @@
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A34" s="6"/>
-      <c r="B34" s="9" t="s">
+      <c r="A34" s="15"/>
+      <c r="B34" s="20" t="s">
         <v>9</v>
       </c>
       <c r="C34" t="s">
@@ -1080,8 +1080,8 @@
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A35" s="6"/>
-      <c r="B35" s="7"/>
+      <c r="A35" s="15"/>
+      <c r="B35" s="18"/>
       <c r="C35" t="s">
         <v>18</v>
       </c>
@@ -1090,8 +1090,8 @@
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A36" s="6"/>
-      <c r="B36" s="7"/>
+      <c r="A36" s="15"/>
+      <c r="B36" s="18"/>
       <c r="C36" t="s">
         <v>19</v>
       </c>
@@ -1100,8 +1100,8 @@
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A37" s="6"/>
-      <c r="B37" s="8"/>
+      <c r="A37" s="15"/>
+      <c r="B37" s="19"/>
       <c r="C37" t="s">
         <v>20</v>
       </c>
@@ -1110,8 +1110,8 @@
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A38" s="6"/>
-      <c r="B38" s="9" t="s">
+      <c r="A38" s="15"/>
+      <c r="B38" s="20" t="s">
         <v>10</v>
       </c>
       <c r="C38" t="s">
@@ -1122,8 +1122,8 @@
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A39" s="6"/>
-      <c r="B39" s="7"/>
+      <c r="A39" s="15"/>
+      <c r="B39" s="18"/>
       <c r="C39" t="s">
         <v>18</v>
       </c>
@@ -1132,8 +1132,8 @@
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A40" s="6"/>
-      <c r="B40" s="7"/>
+      <c r="A40" s="15"/>
+      <c r="B40" s="18"/>
       <c r="C40" t="s">
         <v>19</v>
       </c>
@@ -1142,8 +1142,8 @@
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A41" s="6"/>
-      <c r="B41" s="8"/>
+      <c r="A41" s="15"/>
+      <c r="B41" s="19"/>
       <c r="C41" t="s">
         <v>20</v>
       </c>
@@ -1152,8 +1152,8 @@
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A42" s="6"/>
-      <c r="B42" s="9" t="s">
+      <c r="A42" s="15"/>
+      <c r="B42" s="20" t="s">
         <v>11</v>
       </c>
       <c r="C42" t="s">
@@ -1164,8 +1164,8 @@
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A43" s="6"/>
-      <c r="B43" s="7"/>
+      <c r="A43" s="15"/>
+      <c r="B43" s="18"/>
       <c r="C43" t="s">
         <v>18</v>
       </c>
@@ -1174,8 +1174,8 @@
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A44" s="6"/>
-      <c r="B44" s="7"/>
+      <c r="A44" s="15"/>
+      <c r="B44" s="18"/>
       <c r="C44" t="s">
         <v>19</v>
       </c>
@@ -1184,8 +1184,8 @@
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A45" s="6"/>
-      <c r="B45" s="8"/>
+      <c r="A45" s="15"/>
+      <c r="B45" s="19"/>
       <c r="C45" t="s">
         <v>20</v>
       </c>
@@ -1194,8 +1194,8 @@
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A46" s="6"/>
-      <c r="B46" s="9" t="s">
+      <c r="A46" s="15"/>
+      <c r="B46" s="20" t="s">
         <v>12</v>
       </c>
       <c r="C46" t="s">
@@ -1206,8 +1206,8 @@
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A47" s="6"/>
-      <c r="B47" s="7"/>
+      <c r="A47" s="15"/>
+      <c r="B47" s="18"/>
       <c r="C47" t="s">
         <v>18</v>
       </c>
@@ -1216,8 +1216,8 @@
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A48" s="6"/>
-      <c r="B48" s="7"/>
+      <c r="A48" s="15"/>
+      <c r="B48" s="18"/>
       <c r="C48" t="s">
         <v>19</v>
       </c>
@@ -1226,8 +1226,8 @@
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A49" s="6"/>
-      <c r="B49" s="8"/>
+      <c r="A49" s="15"/>
+      <c r="B49" s="19"/>
       <c r="C49" t="s">
         <v>20</v>
       </c>
@@ -1236,8 +1236,8 @@
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A50" s="6"/>
-      <c r="B50" s="9" t="s">
+      <c r="A50" s="15"/>
+      <c r="B50" s="20" t="s">
         <v>13</v>
       </c>
       <c r="C50" t="s">
@@ -1248,8 +1248,8 @@
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A51" s="6"/>
-      <c r="B51" s="7"/>
+      <c r="A51" s="15"/>
+      <c r="B51" s="18"/>
       <c r="C51" t="s">
         <v>18</v>
       </c>
@@ -1258,8 +1258,8 @@
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A52" s="6"/>
-      <c r="B52" s="7"/>
+      <c r="A52" s="15"/>
+      <c r="B52" s="18"/>
       <c r="C52" t="s">
         <v>19</v>
       </c>
@@ -1268,8 +1268,8 @@
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A53" s="6"/>
-      <c r="B53" s="8"/>
+      <c r="A53" s="15"/>
+      <c r="B53" s="19"/>
       <c r="C53" t="s">
         <v>20</v>
       </c>
@@ -1278,8 +1278,8 @@
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A54" s="6"/>
-      <c r="B54" s="9" t="s">
+      <c r="A54" s="15"/>
+      <c r="B54" s="20" t="s">
         <v>14</v>
       </c>
       <c r="C54" t="s">
@@ -1290,8 +1290,8 @@
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A55" s="6"/>
-      <c r="B55" s="7"/>
+      <c r="A55" s="15"/>
+      <c r="B55" s="18"/>
       <c r="C55" t="s">
         <v>18</v>
       </c>
@@ -1300,8 +1300,8 @@
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A56" s="6"/>
-      <c r="B56" s="7"/>
+      <c r="A56" s="15"/>
+      <c r="B56" s="18"/>
       <c r="C56" t="s">
         <v>19</v>
       </c>
@@ -1310,8 +1310,8 @@
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A57" s="6"/>
-      <c r="B57" s="8"/>
+      <c r="A57" s="15"/>
+      <c r="B57" s="19"/>
       <c r="C57" t="s">
         <v>20</v>
       </c>
@@ -1320,8 +1320,8 @@
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A58" s="6"/>
-      <c r="B58" s="9" t="s">
+      <c r="A58" s="15"/>
+      <c r="B58" s="20" t="s">
         <v>15</v>
       </c>
       <c r="C58" t="s">
@@ -1332,8 +1332,8 @@
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A59" s="6"/>
-      <c r="B59" s="7"/>
+      <c r="A59" s="15"/>
+      <c r="B59" s="18"/>
       <c r="C59" t="s">
         <v>18</v>
       </c>
@@ -1342,8 +1342,8 @@
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A60" s="6"/>
-      <c r="B60" s="7"/>
+      <c r="A60" s="15"/>
+      <c r="B60" s="18"/>
       <c r="C60" t="s">
         <v>19</v>
       </c>
@@ -1352,8 +1352,8 @@
       </c>
     </row>
     <row r="61" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="10"/>
-      <c r="B61" s="11"/>
+      <c r="A61" s="16"/>
+      <c r="B61" s="21"/>
       <c r="C61" t="s">
         <v>20</v>
       </c>
@@ -1362,7 +1362,7 @@
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A62" s="12" t="s">
+      <c r="A62" s="10" t="s">
         <v>6</v>
       </c>
       <c r="B62" s="13" t="s">
@@ -1376,8 +1376,8 @@
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A63" s="14"/>
-      <c r="B63" s="15"/>
+      <c r="A63" s="11"/>
+      <c r="B63" s="7"/>
       <c r="C63" t="s">
         <v>18</v>
       </c>
@@ -1386,8 +1386,8 @@
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A64" s="14"/>
-      <c r="B64" s="15"/>
+      <c r="A64" s="11"/>
+      <c r="B64" s="7"/>
       <c r="C64" t="s">
         <v>19</v>
       </c>
@@ -1396,8 +1396,8 @@
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A65" s="14"/>
-      <c r="B65" s="16"/>
+      <c r="A65" s="11"/>
+      <c r="B65" s="8"/>
       <c r="C65" t="s">
         <v>20</v>
       </c>
@@ -1406,8 +1406,8 @@
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A66" s="14"/>
-      <c r="B66" s="17" t="s">
+      <c r="A66" s="11"/>
+      <c r="B66" s="4" t="s">
         <v>12</v>
       </c>
       <c r="C66" t="s">
@@ -1418,8 +1418,8 @@
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A67" s="14"/>
-      <c r="B67" s="15"/>
+      <c r="A67" s="11"/>
+      <c r="B67" s="7"/>
       <c r="C67" t="s">
         <v>18</v>
       </c>
@@ -1428,8 +1428,8 @@
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A68" s="14"/>
-      <c r="B68" s="15"/>
+      <c r="A68" s="11"/>
+      <c r="B68" s="7"/>
       <c r="C68" t="s">
         <v>19</v>
       </c>
@@ -1438,8 +1438,8 @@
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A69" s="14"/>
-      <c r="B69" s="16"/>
+      <c r="A69" s="11"/>
+      <c r="B69" s="8"/>
       <c r="C69" t="s">
         <v>20</v>
       </c>
@@ -1448,8 +1448,8 @@
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A70" s="14"/>
-      <c r="B70" s="17" t="s">
+      <c r="A70" s="11"/>
+      <c r="B70" s="4" t="s">
         <v>14</v>
       </c>
       <c r="C70" t="s">
@@ -1460,8 +1460,8 @@
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A71" s="14"/>
-      <c r="B71" s="15"/>
+      <c r="A71" s="11"/>
+      <c r="B71" s="7"/>
       <c r="C71" t="s">
         <v>18</v>
       </c>
@@ -1470,8 +1470,8 @@
       </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A72" s="14"/>
-      <c r="B72" s="15"/>
+      <c r="A72" s="11"/>
+      <c r="B72" s="7"/>
       <c r="C72" t="s">
         <v>19</v>
       </c>
@@ -1480,8 +1480,8 @@
       </c>
     </row>
     <row r="73" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A73" s="18"/>
-      <c r="B73" s="19"/>
+      <c r="A73" s="12"/>
+      <c r="B73" s="9"/>
       <c r="C73" t="s">
         <v>20</v>
       </c>
@@ -1490,7 +1490,7 @@
       </c>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A74" s="12" t="s">
+      <c r="A74" s="10" t="s">
         <v>7</v>
       </c>
       <c r="B74" s="13" t="s">
@@ -1504,8 +1504,8 @@
       </c>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A75" s="14"/>
-      <c r="B75" s="15"/>
+      <c r="A75" s="11"/>
+      <c r="B75" s="7"/>
       <c r="C75" t="s">
         <v>18</v>
       </c>
@@ -1514,8 +1514,8 @@
       </c>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A76" s="14"/>
-      <c r="B76" s="15"/>
+      <c r="A76" s="11"/>
+      <c r="B76" s="7"/>
       <c r="C76" t="s">
         <v>19</v>
       </c>
@@ -1524,8 +1524,8 @@
       </c>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A77" s="14"/>
-      <c r="B77" s="16"/>
+      <c r="A77" s="11"/>
+      <c r="B77" s="8"/>
       <c r="C77" t="s">
         <v>20</v>
       </c>
@@ -1534,8 +1534,8 @@
       </c>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A78" s="14"/>
-      <c r="B78" s="17" t="s">
+      <c r="A78" s="11"/>
+      <c r="B78" s="4" t="s">
         <v>9</v>
       </c>
       <c r="C78" t="s">
@@ -1546,8 +1546,8 @@
       </c>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A79" s="14"/>
-      <c r="B79" s="15"/>
+      <c r="A79" s="11"/>
+      <c r="B79" s="7"/>
       <c r="C79" t="s">
         <v>18</v>
       </c>
@@ -1556,8 +1556,8 @@
       </c>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A80" s="14"/>
-      <c r="B80" s="15"/>
+      <c r="A80" s="11"/>
+      <c r="B80" s="7"/>
       <c r="C80" t="s">
         <v>19</v>
       </c>
@@ -1566,8 +1566,8 @@
       </c>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A81" s="14"/>
-      <c r="B81" s="16"/>
+      <c r="A81" s="11"/>
+      <c r="B81" s="8"/>
       <c r="C81" t="s">
         <v>20</v>
       </c>
@@ -1576,8 +1576,8 @@
       </c>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A82" s="14"/>
-      <c r="B82" s="17" t="s">
+      <c r="A82" s="11"/>
+      <c r="B82" s="4" t="s">
         <v>10</v>
       </c>
       <c r="C82" t="s">
@@ -1588,8 +1588,8 @@
       </c>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A83" s="14"/>
-      <c r="B83" s="15"/>
+      <c r="A83" s="11"/>
+      <c r="B83" s="7"/>
       <c r="C83" t="s">
         <v>18</v>
       </c>
@@ -1598,8 +1598,8 @@
       </c>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A84" s="14"/>
-      <c r="B84" s="15"/>
+      <c r="A84" s="11"/>
+      <c r="B84" s="7"/>
       <c r="C84" t="s">
         <v>19</v>
       </c>
@@ -1608,8 +1608,8 @@
       </c>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A85" s="14"/>
-      <c r="B85" s="16"/>
+      <c r="A85" s="11"/>
+      <c r="B85" s="8"/>
       <c r="C85" t="s">
         <v>20</v>
       </c>
@@ -1618,8 +1618,8 @@
       </c>
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A86" s="14"/>
-      <c r="B86" s="17" t="s">
+      <c r="A86" s="11"/>
+      <c r="B86" s="4" t="s">
         <v>11</v>
       </c>
       <c r="C86" t="s">
@@ -1630,8 +1630,8 @@
       </c>
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A87" s="14"/>
-      <c r="B87" s="15"/>
+      <c r="A87" s="11"/>
+      <c r="B87" s="7"/>
       <c r="C87" t="s">
         <v>18</v>
       </c>
@@ -1640,8 +1640,8 @@
       </c>
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A88" s="14"/>
-      <c r="B88" s="15"/>
+      <c r="A88" s="11"/>
+      <c r="B88" s="7"/>
       <c r="C88" t="s">
         <v>19</v>
       </c>
@@ -1650,8 +1650,8 @@
       </c>
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A89" s="14"/>
-      <c r="B89" s="16"/>
+      <c r="A89" s="11"/>
+      <c r="B89" s="8"/>
       <c r="C89" t="s">
         <v>20</v>
       </c>
@@ -1660,8 +1660,8 @@
       </c>
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A90" s="14"/>
-      <c r="B90" s="17" t="s">
+      <c r="A90" s="11"/>
+      <c r="B90" s="4" t="s">
         <v>12</v>
       </c>
       <c r="C90" t="s">
@@ -1672,8 +1672,8 @@
       </c>
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A91" s="14"/>
-      <c r="B91" s="15"/>
+      <c r="A91" s="11"/>
+      <c r="B91" s="7"/>
       <c r="C91" t="s">
         <v>18</v>
       </c>
@@ -1682,8 +1682,8 @@
       </c>
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A92" s="14"/>
-      <c r="B92" s="15"/>
+      <c r="A92" s="11"/>
+      <c r="B92" s="7"/>
       <c r="C92" t="s">
         <v>19</v>
       </c>
@@ -1692,8 +1692,8 @@
       </c>
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A93" s="14"/>
-      <c r="B93" s="16"/>
+      <c r="A93" s="11"/>
+      <c r="B93" s="8"/>
       <c r="C93" t="s">
         <v>20</v>
       </c>
@@ -1702,8 +1702,8 @@
       </c>
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A94" s="14"/>
-      <c r="B94" s="17" t="s">
+      <c r="A94" s="11"/>
+      <c r="B94" s="4" t="s">
         <v>13</v>
       </c>
       <c r="C94" t="s">
@@ -1714,8 +1714,8 @@
       </c>
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A95" s="14"/>
-      <c r="B95" s="15"/>
+      <c r="A95" s="11"/>
+      <c r="B95" s="7"/>
       <c r="C95" t="s">
         <v>18</v>
       </c>
@@ -1724,8 +1724,8 @@
       </c>
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A96" s="14"/>
-      <c r="B96" s="15"/>
+      <c r="A96" s="11"/>
+      <c r="B96" s="7"/>
       <c r="C96" t="s">
         <v>19</v>
       </c>
@@ -1734,8 +1734,8 @@
       </c>
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A97" s="14"/>
-      <c r="B97" s="16"/>
+      <c r="A97" s="11"/>
+      <c r="B97" s="8"/>
       <c r="C97" t="s">
         <v>20</v>
       </c>
@@ -1744,8 +1744,8 @@
       </c>
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A98" s="14"/>
-      <c r="B98" s="17" t="s">
+      <c r="A98" s="11"/>
+      <c r="B98" s="4" t="s">
         <v>14</v>
       </c>
       <c r="C98" t="s">
@@ -1756,8 +1756,8 @@
       </c>
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A99" s="14"/>
-      <c r="B99" s="15"/>
+      <c r="A99" s="11"/>
+      <c r="B99" s="7"/>
       <c r="C99" t="s">
         <v>18</v>
       </c>
@@ -1766,8 +1766,8 @@
       </c>
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A100" s="14"/>
-      <c r="B100" s="15"/>
+      <c r="A100" s="11"/>
+      <c r="B100" s="7"/>
       <c r="C100" t="s">
         <v>19</v>
       </c>
@@ -1776,8 +1776,8 @@
       </c>
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A101" s="14"/>
-      <c r="B101" s="16"/>
+      <c r="A101" s="11"/>
+      <c r="B101" s="8"/>
       <c r="C101" t="s">
         <v>20</v>
       </c>
@@ -1786,8 +1786,8 @@
       </c>
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A102" s="14"/>
-      <c r="B102" s="17" t="s">
+      <c r="A102" s="11"/>
+      <c r="B102" s="4" t="s">
         <v>15</v>
       </c>
       <c r="C102" t="s">
@@ -1798,8 +1798,8 @@
       </c>
     </row>
     <row r="103" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A103" s="14"/>
-      <c r="B103" s="15"/>
+      <c r="A103" s="11"/>
+      <c r="B103" s="7"/>
       <c r="C103" t="s">
         <v>18</v>
       </c>
@@ -1808,8 +1808,8 @@
       </c>
     </row>
     <row r="104" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A104" s="14"/>
-      <c r="B104" s="15"/>
+      <c r="A104" s="11"/>
+      <c r="B104" s="7"/>
       <c r="C104" t="s">
         <v>19</v>
       </c>
@@ -1818,8 +1818,8 @@
       </c>
     </row>
     <row r="105" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A105" s="18"/>
-      <c r="B105" s="19"/>
+      <c r="A105" s="12"/>
+      <c r="B105" s="9"/>
       <c r="C105" t="s">
         <v>20</v>
       </c>
@@ -1828,7 +1828,7 @@
       </c>
     </row>
     <row r="106" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A106" s="12" t="s">
+      <c r="A106" s="10" t="s">
         <v>8</v>
       </c>
       <c r="B106" s="13" t="s">
@@ -1842,8 +1842,8 @@
       </c>
     </row>
     <row r="107" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A107" s="14"/>
-      <c r="B107" s="15"/>
+      <c r="A107" s="11"/>
+      <c r="B107" s="7"/>
       <c r="C107" t="s">
         <v>18</v>
       </c>
@@ -1852,8 +1852,8 @@
       </c>
     </row>
     <row r="108" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A108" s="14"/>
-      <c r="B108" s="15"/>
+      <c r="A108" s="11"/>
+      <c r="B108" s="7"/>
       <c r="C108" t="s">
         <v>19</v>
       </c>
@@ -1862,8 +1862,8 @@
       </c>
     </row>
     <row r="109" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A109" s="14"/>
-      <c r="B109" s="16"/>
+      <c r="A109" s="11"/>
+      <c r="B109" s="8"/>
       <c r="C109" t="s">
         <v>20</v>
       </c>
@@ -1872,8 +1872,8 @@
       </c>
     </row>
     <row r="110" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A110" s="14"/>
-      <c r="B110" s="17" t="s">
+      <c r="A110" s="11"/>
+      <c r="B110" s="4" t="s">
         <v>9</v>
       </c>
       <c r="C110" t="s">
@@ -1884,8 +1884,8 @@
       </c>
     </row>
     <row r="111" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A111" s="14"/>
-      <c r="B111" s="15"/>
+      <c r="A111" s="11"/>
+      <c r="B111" s="7"/>
       <c r="C111" t="s">
         <v>18</v>
       </c>
@@ -1894,8 +1894,8 @@
       </c>
     </row>
     <row r="112" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A112" s="14"/>
-      <c r="B112" s="15"/>
+      <c r="A112" s="11"/>
+      <c r="B112" s="7"/>
       <c r="C112" t="s">
         <v>19</v>
       </c>
@@ -1904,8 +1904,8 @@
       </c>
     </row>
     <row r="113" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A113" s="14"/>
-      <c r="B113" s="16"/>
+      <c r="A113" s="11"/>
+      <c r="B113" s="8"/>
       <c r="C113" t="s">
         <v>20</v>
       </c>
@@ -1914,8 +1914,8 @@
       </c>
     </row>
     <row r="114" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A114" s="14"/>
-      <c r="B114" s="17" t="s">
+      <c r="A114" s="11"/>
+      <c r="B114" s="4" t="s">
         <v>10</v>
       </c>
       <c r="C114" t="s">
@@ -1926,8 +1926,8 @@
       </c>
     </row>
     <row r="115" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A115" s="14"/>
-      <c r="B115" s="15"/>
+      <c r="A115" s="11"/>
+      <c r="B115" s="7"/>
       <c r="C115" t="s">
         <v>18</v>
       </c>
@@ -1936,8 +1936,8 @@
       </c>
     </row>
     <row r="116" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A116" s="14"/>
-      <c r="B116" s="15"/>
+      <c r="A116" s="11"/>
+      <c r="B116" s="7"/>
       <c r="C116" t="s">
         <v>19</v>
       </c>
@@ -1946,8 +1946,8 @@
       </c>
     </row>
     <row r="117" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A117" s="14"/>
-      <c r="B117" s="16"/>
+      <c r="A117" s="11"/>
+      <c r="B117" s="8"/>
       <c r="C117" t="s">
         <v>20</v>
       </c>
@@ -1956,8 +1956,8 @@
       </c>
     </row>
     <row r="118" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A118" s="14"/>
-      <c r="B118" s="17" t="s">
+      <c r="A118" s="11"/>
+      <c r="B118" s="4" t="s">
         <v>11</v>
       </c>
       <c r="C118" t="s">
@@ -1968,8 +1968,8 @@
       </c>
     </row>
     <row r="119" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A119" s="14"/>
-      <c r="B119" s="15"/>
+      <c r="A119" s="11"/>
+      <c r="B119" s="7"/>
       <c r="C119" t="s">
         <v>18</v>
       </c>
@@ -1978,8 +1978,8 @@
       </c>
     </row>
     <row r="120" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A120" s="14"/>
-      <c r="B120" s="15"/>
+      <c r="A120" s="11"/>
+      <c r="B120" s="7"/>
       <c r="C120" t="s">
         <v>19</v>
       </c>
@@ -1988,8 +1988,8 @@
       </c>
     </row>
     <row r="121" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A121" s="14"/>
-      <c r="B121" s="16"/>
+      <c r="A121" s="11"/>
+      <c r="B121" s="8"/>
       <c r="C121" t="s">
         <v>20</v>
       </c>
@@ -1998,8 +1998,8 @@
       </c>
     </row>
     <row r="122" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A122" s="14"/>
-      <c r="B122" s="17" t="s">
+      <c r="A122" s="11"/>
+      <c r="B122" s="4" t="s">
         <v>12</v>
       </c>
       <c r="C122" t="s">
@@ -2010,8 +2010,8 @@
       </c>
     </row>
     <row r="123" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A123" s="14"/>
-      <c r="B123" s="15"/>
+      <c r="A123" s="11"/>
+      <c r="B123" s="7"/>
       <c r="C123" t="s">
         <v>18</v>
       </c>
@@ -2020,8 +2020,8 @@
       </c>
     </row>
     <row r="124" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A124" s="14"/>
-      <c r="B124" s="15"/>
+      <c r="A124" s="11"/>
+      <c r="B124" s="7"/>
       <c r="C124" t="s">
         <v>19</v>
       </c>
@@ -2030,8 +2030,8 @@
       </c>
     </row>
     <row r="125" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A125" s="14"/>
-      <c r="B125" s="16"/>
+      <c r="A125" s="11"/>
+      <c r="B125" s="8"/>
       <c r="C125" t="s">
         <v>20</v>
       </c>
@@ -2040,8 +2040,8 @@
       </c>
     </row>
     <row r="126" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A126" s="14"/>
-      <c r="B126" s="17" t="s">
+      <c r="A126" s="11"/>
+      <c r="B126" s="4" t="s">
         <v>13</v>
       </c>
       <c r="C126" t="s">
@@ -2052,8 +2052,8 @@
       </c>
     </row>
     <row r="127" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A127" s="14"/>
-      <c r="B127" s="15"/>
+      <c r="A127" s="11"/>
+      <c r="B127" s="7"/>
       <c r="C127" t="s">
         <v>18</v>
       </c>
@@ -2062,8 +2062,8 @@
       </c>
     </row>
     <row r="128" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A128" s="14"/>
-      <c r="B128" s="15"/>
+      <c r="A128" s="11"/>
+      <c r="B128" s="7"/>
       <c r="C128" t="s">
         <v>19</v>
       </c>
@@ -2072,8 +2072,8 @@
       </c>
     </row>
     <row r="129" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A129" s="14"/>
-      <c r="B129" s="16"/>
+      <c r="A129" s="11"/>
+      <c r="B129" s="8"/>
       <c r="C129" t="s">
         <v>20</v>
       </c>
@@ -2082,8 +2082,8 @@
       </c>
     </row>
     <row r="130" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A130" s="14"/>
-      <c r="B130" s="17" t="s">
+      <c r="A130" s="11"/>
+      <c r="B130" s="4" t="s">
         <v>14</v>
       </c>
       <c r="C130" t="s">
@@ -2094,8 +2094,8 @@
       </c>
     </row>
     <row r="131" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A131" s="14"/>
-      <c r="B131" s="20"/>
+      <c r="A131" s="11"/>
+      <c r="B131" s="5"/>
       <c r="C131" t="s">
         <v>18</v>
       </c>
@@ -2104,8 +2104,8 @@
       </c>
     </row>
     <row r="132" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A132" s="14"/>
-      <c r="B132" s="20"/>
+      <c r="A132" s="11"/>
+      <c r="B132" s="5"/>
       <c r="C132" t="s">
         <v>19</v>
       </c>
@@ -2114,8 +2114,8 @@
       </c>
     </row>
     <row r="133" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A133" s="18"/>
-      <c r="B133" s="21"/>
+      <c r="A133" s="12"/>
+      <c r="B133" s="6"/>
       <c r="C133" t="s">
         <v>20</v>
       </c>
@@ -2125,6 +2125,33 @@
     </row>
   </sheetData>
   <mergeCells count="38">
+    <mergeCell ref="A2:A29"/>
+    <mergeCell ref="B2:B5"/>
+    <mergeCell ref="B6:B9"/>
+    <mergeCell ref="B10:B13"/>
+    <mergeCell ref="B14:B17"/>
+    <mergeCell ref="B18:B21"/>
+    <mergeCell ref="B22:B25"/>
+    <mergeCell ref="B26:B29"/>
+    <mergeCell ref="A30:A61"/>
+    <mergeCell ref="B30:B33"/>
+    <mergeCell ref="B34:B37"/>
+    <mergeCell ref="B38:B41"/>
+    <mergeCell ref="B42:B45"/>
+    <mergeCell ref="B46:B49"/>
+    <mergeCell ref="B50:B53"/>
+    <mergeCell ref="B54:B57"/>
+    <mergeCell ref="B58:B61"/>
+    <mergeCell ref="A62:A73"/>
+    <mergeCell ref="B62:B65"/>
+    <mergeCell ref="B66:B69"/>
+    <mergeCell ref="B70:B73"/>
+    <mergeCell ref="A74:A105"/>
+    <mergeCell ref="B74:B77"/>
+    <mergeCell ref="B78:B81"/>
+    <mergeCell ref="B82:B85"/>
+    <mergeCell ref="B86:B89"/>
+    <mergeCell ref="B90:B93"/>
     <mergeCell ref="B130:B133"/>
     <mergeCell ref="B94:B97"/>
     <mergeCell ref="B98:B101"/>
@@ -2136,36 +2163,9 @@
     <mergeCell ref="B118:B121"/>
     <mergeCell ref="B122:B125"/>
     <mergeCell ref="B126:B129"/>
-    <mergeCell ref="A62:A73"/>
-    <mergeCell ref="B62:B65"/>
-    <mergeCell ref="B66:B69"/>
-    <mergeCell ref="B70:B73"/>
-    <mergeCell ref="A74:A105"/>
-    <mergeCell ref="B74:B77"/>
-    <mergeCell ref="B78:B81"/>
-    <mergeCell ref="B82:B85"/>
-    <mergeCell ref="B86:B89"/>
-    <mergeCell ref="B90:B93"/>
-    <mergeCell ref="A30:A61"/>
-    <mergeCell ref="B30:B33"/>
-    <mergeCell ref="B34:B37"/>
-    <mergeCell ref="B38:B41"/>
-    <mergeCell ref="B42:B45"/>
-    <mergeCell ref="B46:B49"/>
-    <mergeCell ref="B50:B53"/>
-    <mergeCell ref="B54:B57"/>
-    <mergeCell ref="B58:B61"/>
-    <mergeCell ref="A2:A29"/>
-    <mergeCell ref="B2:B5"/>
-    <mergeCell ref="B6:B9"/>
-    <mergeCell ref="B10:B13"/>
-    <mergeCell ref="B14:B17"/>
-    <mergeCell ref="B18:B21"/>
-    <mergeCell ref="B22:B25"/>
-    <mergeCell ref="B26:B29"/>
   </mergeCells>
   <conditionalFormatting sqref="D2:D133">
-    <cfRule type="cellIs" dxfId="0" priority="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="1" priority="1" operator="greaterThan">
       <formula>0.3</formula>
     </cfRule>
   </conditionalFormatting>
@@ -2193,10 +2193,10 @@
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A2" s="4" t="s">
+      <c r="A2" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="17" t="s">
         <v>9</v>
       </c>
       <c r="C2" t="s">
@@ -2207,8 +2207,8 @@
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A3" s="6"/>
-      <c r="B3" s="7"/>
+      <c r="A3" s="15"/>
+      <c r="B3" s="18"/>
       <c r="C3" t="s">
         <v>18</v>
       </c>
@@ -2217,8 +2217,8 @@
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A4" s="6"/>
-      <c r="B4" s="7"/>
+      <c r="A4" s="15"/>
+      <c r="B4" s="18"/>
       <c r="C4" t="s">
         <v>19</v>
       </c>
@@ -2227,8 +2227,8 @@
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A5" s="6"/>
-      <c r="B5" s="8"/>
+      <c r="A5" s="15"/>
+      <c r="B5" s="19"/>
       <c r="C5" t="s">
         <v>20</v>
       </c>
@@ -2237,8 +2237,8 @@
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A6" s="6"/>
-      <c r="B6" s="9" t="s">
+      <c r="A6" s="15"/>
+      <c r="B6" s="20" t="s">
         <v>10</v>
       </c>
       <c r="C6" t="s">
@@ -2249,8 +2249,8 @@
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A7" s="6"/>
-      <c r="B7" s="7"/>
+      <c r="A7" s="15"/>
+      <c r="B7" s="18"/>
       <c r="C7" t="s">
         <v>18</v>
       </c>
@@ -2259,8 +2259,8 @@
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A8" s="6"/>
-      <c r="B8" s="7"/>
+      <c r="A8" s="15"/>
+      <c r="B8" s="18"/>
       <c r="C8" t="s">
         <v>19</v>
       </c>
@@ -2269,8 +2269,8 @@
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A9" s="6"/>
-      <c r="B9" s="8"/>
+      <c r="A9" s="15"/>
+      <c r="B9" s="19"/>
       <c r="C9" t="s">
         <v>20</v>
       </c>
@@ -2279,8 +2279,8 @@
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A10" s="6"/>
-      <c r="B10" s="9" t="s">
+      <c r="A10" s="15"/>
+      <c r="B10" s="20" t="s">
         <v>11</v>
       </c>
       <c r="C10" t="s">
@@ -2291,8 +2291,8 @@
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A11" s="6"/>
-      <c r="B11" s="7"/>
+      <c r="A11" s="15"/>
+      <c r="B11" s="18"/>
       <c r="C11" t="s">
         <v>18</v>
       </c>
@@ -2301,8 +2301,8 @@
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A12" s="6"/>
-      <c r="B12" s="7"/>
+      <c r="A12" s="15"/>
+      <c r="B12" s="18"/>
       <c r="C12" t="s">
         <v>19</v>
       </c>
@@ -2311,8 +2311,8 @@
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A13" s="6"/>
-      <c r="B13" s="8"/>
+      <c r="A13" s="15"/>
+      <c r="B13" s="19"/>
       <c r="C13" t="s">
         <v>20</v>
       </c>
@@ -2321,8 +2321,8 @@
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A14" s="6"/>
-      <c r="B14" s="9" t="s">
+      <c r="A14" s="15"/>
+      <c r="B14" s="20" t="s">
         <v>12</v>
       </c>
       <c r="C14" t="s">
@@ -2333,8 +2333,8 @@
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A15" s="6"/>
-      <c r="B15" s="7"/>
+      <c r="A15" s="15"/>
+      <c r="B15" s="18"/>
       <c r="C15" t="s">
         <v>18</v>
       </c>
@@ -2343,8 +2343,8 @@
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A16" s="6"/>
-      <c r="B16" s="7"/>
+      <c r="A16" s="15"/>
+      <c r="B16" s="18"/>
       <c r="C16" t="s">
         <v>19</v>
       </c>
@@ -2353,8 +2353,8 @@
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A17" s="6"/>
-      <c r="B17" s="8"/>
+      <c r="A17" s="15"/>
+      <c r="B17" s="19"/>
       <c r="C17" t="s">
         <v>20</v>
       </c>
@@ -2363,8 +2363,8 @@
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A18" s="6"/>
-      <c r="B18" s="9" t="s">
+      <c r="A18" s="15"/>
+      <c r="B18" s="20" t="s">
         <v>13</v>
       </c>
       <c r="C18" t="s">
@@ -2375,8 +2375,8 @@
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A19" s="6"/>
-      <c r="B19" s="7"/>
+      <c r="A19" s="15"/>
+      <c r="B19" s="18"/>
       <c r="C19" t="s">
         <v>18</v>
       </c>
@@ -2385,8 +2385,8 @@
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A20" s="6"/>
-      <c r="B20" s="7"/>
+      <c r="A20" s="15"/>
+      <c r="B20" s="18"/>
       <c r="C20" t="s">
         <v>19</v>
       </c>
@@ -2395,8 +2395,8 @@
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A21" s="6"/>
-      <c r="B21" s="8"/>
+      <c r="A21" s="15"/>
+      <c r="B21" s="19"/>
       <c r="C21" t="s">
         <v>20</v>
       </c>
@@ -2405,8 +2405,8 @@
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A22" s="6"/>
-      <c r="B22" s="9" t="s">
+      <c r="A22" s="15"/>
+      <c r="B22" s="20" t="s">
         <v>14</v>
       </c>
       <c r="C22" t="s">
@@ -2417,8 +2417,8 @@
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A23" s="6"/>
-      <c r="B23" s="7"/>
+      <c r="A23" s="15"/>
+      <c r="B23" s="18"/>
       <c r="C23" t="s">
         <v>18</v>
       </c>
@@ -2427,8 +2427,8 @@
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A24" s="6"/>
-      <c r="B24" s="7"/>
+      <c r="A24" s="15"/>
+      <c r="B24" s="18"/>
       <c r="C24" t="s">
         <v>19</v>
       </c>
@@ -2437,8 +2437,8 @@
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A25" s="6"/>
-      <c r="B25" s="8"/>
+      <c r="A25" s="15"/>
+      <c r="B25" s="19"/>
       <c r="C25" t="s">
         <v>20</v>
       </c>
@@ -2447,8 +2447,8 @@
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A26" s="6"/>
-      <c r="B26" s="9" t="s">
+      <c r="A26" s="15"/>
+      <c r="B26" s="20" t="s">
         <v>15</v>
       </c>
       <c r="C26" t="s">
@@ -2459,8 +2459,8 @@
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A27" s="6"/>
-      <c r="B27" s="7"/>
+      <c r="A27" s="15"/>
+      <c r="B27" s="18"/>
       <c r="C27" t="s">
         <v>18</v>
       </c>
@@ -2469,8 +2469,8 @@
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A28" s="6"/>
-      <c r="B28" s="7"/>
+      <c r="A28" s="15"/>
+      <c r="B28" s="18"/>
       <c r="C28" t="s">
         <v>19</v>
       </c>
@@ -2479,8 +2479,8 @@
       </c>
     </row>
     <row r="29" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="10"/>
-      <c r="B29" s="11"/>
+      <c r="A29" s="16"/>
+      <c r="B29" s="21"/>
       <c r="C29" t="s">
         <v>20</v>
       </c>
@@ -2489,10 +2489,10 @@
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A30" s="4" t="s">
+      <c r="A30" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="B30" s="5" t="s">
+      <c r="B30" s="17" t="s">
         <v>16</v>
       </c>
       <c r="C30" t="s">
@@ -2503,8 +2503,8 @@
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A31" s="6"/>
-      <c r="B31" s="7"/>
+      <c r="A31" s="15"/>
+      <c r="B31" s="18"/>
       <c r="C31" t="s">
         <v>18</v>
       </c>
@@ -2513,8 +2513,8 @@
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A32" s="6"/>
-      <c r="B32" s="7"/>
+      <c r="A32" s="15"/>
+      <c r="B32" s="18"/>
       <c r="C32" t="s">
         <v>19</v>
       </c>
@@ -2523,8 +2523,8 @@
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A33" s="6"/>
-      <c r="B33" s="8"/>
+      <c r="A33" s="15"/>
+      <c r="B33" s="19"/>
       <c r="C33" t="s">
         <v>20</v>
       </c>
@@ -2533,8 +2533,8 @@
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A34" s="6"/>
-      <c r="B34" s="9" t="s">
+      <c r="A34" s="15"/>
+      <c r="B34" s="20" t="s">
         <v>9</v>
       </c>
       <c r="C34" t="s">
@@ -2545,8 +2545,8 @@
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A35" s="6"/>
-      <c r="B35" s="7"/>
+      <c r="A35" s="15"/>
+      <c r="B35" s="18"/>
       <c r="C35" t="s">
         <v>18</v>
       </c>
@@ -2555,8 +2555,8 @@
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A36" s="6"/>
-      <c r="B36" s="7"/>
+      <c r="A36" s="15"/>
+      <c r="B36" s="18"/>
       <c r="C36" t="s">
         <v>19</v>
       </c>
@@ -2565,8 +2565,8 @@
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A37" s="6"/>
-      <c r="B37" s="8"/>
+      <c r="A37" s="15"/>
+      <c r="B37" s="19"/>
       <c r="C37" t="s">
         <v>20</v>
       </c>
@@ -2575,8 +2575,8 @@
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A38" s="6"/>
-      <c r="B38" s="9" t="s">
+      <c r="A38" s="15"/>
+      <c r="B38" s="20" t="s">
         <v>10</v>
       </c>
       <c r="C38" t="s">
@@ -2587,8 +2587,8 @@
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A39" s="6"/>
-      <c r="B39" s="7"/>
+      <c r="A39" s="15"/>
+      <c r="B39" s="18"/>
       <c r="C39" t="s">
         <v>18</v>
       </c>
@@ -2597,8 +2597,8 @@
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A40" s="6"/>
-      <c r="B40" s="7"/>
+      <c r="A40" s="15"/>
+      <c r="B40" s="18"/>
       <c r="C40" t="s">
         <v>19</v>
       </c>
@@ -2607,8 +2607,8 @@
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A41" s="6"/>
-      <c r="B41" s="8"/>
+      <c r="A41" s="15"/>
+      <c r="B41" s="19"/>
       <c r="C41" t="s">
         <v>20</v>
       </c>
@@ -2617,8 +2617,8 @@
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A42" s="6"/>
-      <c r="B42" s="9" t="s">
+      <c r="A42" s="15"/>
+      <c r="B42" s="20" t="s">
         <v>11</v>
       </c>
       <c r="C42" t="s">
@@ -2629,8 +2629,8 @@
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A43" s="6"/>
-      <c r="B43" s="7"/>
+      <c r="A43" s="15"/>
+      <c r="B43" s="18"/>
       <c r="C43" t="s">
         <v>18</v>
       </c>
@@ -2639,8 +2639,8 @@
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A44" s="6"/>
-      <c r="B44" s="7"/>
+      <c r="A44" s="15"/>
+      <c r="B44" s="18"/>
       <c r="C44" t="s">
         <v>19</v>
       </c>
@@ -2649,8 +2649,8 @@
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A45" s="6"/>
-      <c r="B45" s="8"/>
+      <c r="A45" s="15"/>
+      <c r="B45" s="19"/>
       <c r="C45" t="s">
         <v>20</v>
       </c>
@@ -2659,8 +2659,8 @@
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A46" s="6"/>
-      <c r="B46" s="9" t="s">
+      <c r="A46" s="15"/>
+      <c r="B46" s="20" t="s">
         <v>12</v>
       </c>
       <c r="C46" t="s">
@@ -2671,8 +2671,8 @@
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A47" s="6"/>
-      <c r="B47" s="7"/>
+      <c r="A47" s="15"/>
+      <c r="B47" s="18"/>
       <c r="C47" t="s">
         <v>18</v>
       </c>
@@ -2681,8 +2681,8 @@
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A48" s="6"/>
-      <c r="B48" s="7"/>
+      <c r="A48" s="15"/>
+      <c r="B48" s="18"/>
       <c r="C48" t="s">
         <v>19</v>
       </c>
@@ -2691,8 +2691,8 @@
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A49" s="6"/>
-      <c r="B49" s="8"/>
+      <c r="A49" s="15"/>
+      <c r="B49" s="19"/>
       <c r="C49" t="s">
         <v>20</v>
       </c>
@@ -2701,8 +2701,8 @@
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A50" s="6"/>
-      <c r="B50" s="9" t="s">
+      <c r="A50" s="15"/>
+      <c r="B50" s="20" t="s">
         <v>13</v>
       </c>
       <c r="C50" t="s">
@@ -2713,8 +2713,8 @@
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A51" s="6"/>
-      <c r="B51" s="7"/>
+      <c r="A51" s="15"/>
+      <c r="B51" s="18"/>
       <c r="C51" t="s">
         <v>18</v>
       </c>
@@ -2723,8 +2723,8 @@
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A52" s="6"/>
-      <c r="B52" s="7"/>
+      <c r="A52" s="15"/>
+      <c r="B52" s="18"/>
       <c r="C52" t="s">
         <v>19</v>
       </c>
@@ -2733,8 +2733,8 @@
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A53" s="6"/>
-      <c r="B53" s="8"/>
+      <c r="A53" s="15"/>
+      <c r="B53" s="19"/>
       <c r="C53" t="s">
         <v>20</v>
       </c>
@@ -2743,8 +2743,8 @@
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A54" s="6"/>
-      <c r="B54" s="9" t="s">
+      <c r="A54" s="15"/>
+      <c r="B54" s="20" t="s">
         <v>14</v>
       </c>
       <c r="C54" t="s">
@@ -2755,8 +2755,8 @@
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A55" s="6"/>
-      <c r="B55" s="7"/>
+      <c r="A55" s="15"/>
+      <c r="B55" s="18"/>
       <c r="C55" t="s">
         <v>18</v>
       </c>
@@ -2765,8 +2765,8 @@
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A56" s="6"/>
-      <c r="B56" s="7"/>
+      <c r="A56" s="15"/>
+      <c r="B56" s="18"/>
       <c r="C56" t="s">
         <v>19</v>
       </c>
@@ -2775,8 +2775,8 @@
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A57" s="6"/>
-      <c r="B57" s="8"/>
+      <c r="A57" s="15"/>
+      <c r="B57" s="19"/>
       <c r="C57" t="s">
         <v>20</v>
       </c>
@@ -2785,8 +2785,8 @@
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A58" s="6"/>
-      <c r="B58" s="9" t="s">
+      <c r="A58" s="15"/>
+      <c r="B58" s="20" t="s">
         <v>15</v>
       </c>
       <c r="C58" t="s">
@@ -2797,8 +2797,8 @@
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A59" s="6"/>
-      <c r="B59" s="7"/>
+      <c r="A59" s="15"/>
+      <c r="B59" s="18"/>
       <c r="C59" t="s">
         <v>18</v>
       </c>
@@ -2807,8 +2807,8 @@
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A60" s="6"/>
-      <c r="B60" s="7"/>
+      <c r="A60" s="15"/>
+      <c r="B60" s="18"/>
       <c r="C60" t="s">
         <v>19</v>
       </c>
@@ -2817,8 +2817,8 @@
       </c>
     </row>
     <row r="61" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="10"/>
-      <c r="B61" s="11"/>
+      <c r="A61" s="16"/>
+      <c r="B61" s="21"/>
       <c r="C61" t="s">
         <v>20</v>
       </c>
@@ -2827,7 +2827,7 @@
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A62" s="12" t="s">
+      <c r="A62" s="10" t="s">
         <v>6</v>
       </c>
       <c r="B62" s="13" t="s">
@@ -2841,8 +2841,8 @@
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A63" s="14"/>
-      <c r="B63" s="15"/>
+      <c r="A63" s="11"/>
+      <c r="B63" s="7"/>
       <c r="C63" t="s">
         <v>18</v>
       </c>
@@ -2851,8 +2851,8 @@
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A64" s="14"/>
-      <c r="B64" s="15"/>
+      <c r="A64" s="11"/>
+      <c r="B64" s="7"/>
       <c r="C64" t="s">
         <v>19</v>
       </c>
@@ -2861,8 +2861,8 @@
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A65" s="14"/>
-      <c r="B65" s="16"/>
+      <c r="A65" s="11"/>
+      <c r="B65" s="8"/>
       <c r="C65" t="s">
         <v>20</v>
       </c>
@@ -2871,8 +2871,8 @@
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A66" s="14"/>
-      <c r="B66" s="17" t="s">
+      <c r="A66" s="11"/>
+      <c r="B66" s="4" t="s">
         <v>12</v>
       </c>
       <c r="C66" t="s">
@@ -2883,8 +2883,8 @@
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A67" s="14"/>
-      <c r="B67" s="15"/>
+      <c r="A67" s="11"/>
+      <c r="B67" s="7"/>
       <c r="C67" t="s">
         <v>18</v>
       </c>
@@ -2893,8 +2893,8 @@
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A68" s="14"/>
-      <c r="B68" s="15"/>
+      <c r="A68" s="11"/>
+      <c r="B68" s="7"/>
       <c r="C68" t="s">
         <v>19</v>
       </c>
@@ -2903,8 +2903,8 @@
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A69" s="14"/>
-      <c r="B69" s="16"/>
+      <c r="A69" s="11"/>
+      <c r="B69" s="8"/>
       <c r="C69" t="s">
         <v>20</v>
       </c>
@@ -2913,8 +2913,8 @@
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A70" s="14"/>
-      <c r="B70" s="17" t="s">
+      <c r="A70" s="11"/>
+      <c r="B70" s="4" t="s">
         <v>14</v>
       </c>
       <c r="C70" t="s">
@@ -2925,8 +2925,8 @@
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A71" s="14"/>
-      <c r="B71" s="15"/>
+      <c r="A71" s="11"/>
+      <c r="B71" s="7"/>
       <c r="C71" t="s">
         <v>18</v>
       </c>
@@ -2935,8 +2935,8 @@
       </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A72" s="14"/>
-      <c r="B72" s="15"/>
+      <c r="A72" s="11"/>
+      <c r="B72" s="7"/>
       <c r="C72" t="s">
         <v>19</v>
       </c>
@@ -2945,8 +2945,8 @@
       </c>
     </row>
     <row r="73" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A73" s="18"/>
-      <c r="B73" s="19"/>
+      <c r="A73" s="12"/>
+      <c r="B73" s="9"/>
       <c r="C73" t="s">
         <v>20</v>
       </c>
@@ -2955,7 +2955,7 @@
       </c>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A74" s="12" t="s">
+      <c r="A74" s="10" t="s">
         <v>7</v>
       </c>
       <c r="B74" s="13" t="s">
@@ -2969,8 +2969,8 @@
       </c>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A75" s="14"/>
-      <c r="B75" s="15"/>
+      <c r="A75" s="11"/>
+      <c r="B75" s="7"/>
       <c r="C75" t="s">
         <v>18</v>
       </c>
@@ -2979,8 +2979,8 @@
       </c>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A76" s="14"/>
-      <c r="B76" s="15"/>
+      <c r="A76" s="11"/>
+      <c r="B76" s="7"/>
       <c r="C76" t="s">
         <v>19</v>
       </c>
@@ -2989,8 +2989,8 @@
       </c>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A77" s="14"/>
-      <c r="B77" s="16"/>
+      <c r="A77" s="11"/>
+      <c r="B77" s="8"/>
       <c r="C77" t="s">
         <v>20</v>
       </c>
@@ -2999,8 +2999,8 @@
       </c>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A78" s="14"/>
-      <c r="B78" s="17" t="s">
+      <c r="A78" s="11"/>
+      <c r="B78" s="4" t="s">
         <v>9</v>
       </c>
       <c r="C78" t="s">
@@ -3011,8 +3011,8 @@
       </c>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A79" s="14"/>
-      <c r="B79" s="15"/>
+      <c r="A79" s="11"/>
+      <c r="B79" s="7"/>
       <c r="C79" t="s">
         <v>18</v>
       </c>
@@ -3021,8 +3021,8 @@
       </c>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A80" s="14"/>
-      <c r="B80" s="15"/>
+      <c r="A80" s="11"/>
+      <c r="B80" s="7"/>
       <c r="C80" t="s">
         <v>19</v>
       </c>
@@ -3031,8 +3031,8 @@
       </c>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A81" s="14"/>
-      <c r="B81" s="16"/>
+      <c r="A81" s="11"/>
+      <c r="B81" s="8"/>
       <c r="C81" t="s">
         <v>20</v>
       </c>
@@ -3041,8 +3041,8 @@
       </c>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A82" s="14"/>
-      <c r="B82" s="17" t="s">
+      <c r="A82" s="11"/>
+      <c r="B82" s="4" t="s">
         <v>10</v>
       </c>
       <c r="C82" t="s">
@@ -3053,8 +3053,8 @@
       </c>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A83" s="14"/>
-      <c r="B83" s="15"/>
+      <c r="A83" s="11"/>
+      <c r="B83" s="7"/>
       <c r="C83" t="s">
         <v>18</v>
       </c>
@@ -3063,8 +3063,8 @@
       </c>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A84" s="14"/>
-      <c r="B84" s="15"/>
+      <c r="A84" s="11"/>
+      <c r="B84" s="7"/>
       <c r="C84" t="s">
         <v>19</v>
       </c>
@@ -3073,8 +3073,8 @@
       </c>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A85" s="14"/>
-      <c r="B85" s="16"/>
+      <c r="A85" s="11"/>
+      <c r="B85" s="8"/>
       <c r="C85" t="s">
         <v>20</v>
       </c>
@@ -3083,8 +3083,8 @@
       </c>
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A86" s="14"/>
-      <c r="B86" s="17" t="s">
+      <c r="A86" s="11"/>
+      <c r="B86" s="4" t="s">
         <v>11</v>
       </c>
       <c r="C86" t="s">
@@ -3095,8 +3095,8 @@
       </c>
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A87" s="14"/>
-      <c r="B87" s="15"/>
+      <c r="A87" s="11"/>
+      <c r="B87" s="7"/>
       <c r="C87" t="s">
         <v>18</v>
       </c>
@@ -3105,8 +3105,8 @@
       </c>
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A88" s="14"/>
-      <c r="B88" s="15"/>
+      <c r="A88" s="11"/>
+      <c r="B88" s="7"/>
       <c r="C88" t="s">
         <v>19</v>
       </c>
@@ -3115,8 +3115,8 @@
       </c>
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A89" s="14"/>
-      <c r="B89" s="16"/>
+      <c r="A89" s="11"/>
+      <c r="B89" s="8"/>
       <c r="C89" t="s">
         <v>20</v>
       </c>
@@ -3125,8 +3125,8 @@
       </c>
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A90" s="14"/>
-      <c r="B90" s="17" t="s">
+      <c r="A90" s="11"/>
+      <c r="B90" s="4" t="s">
         <v>12</v>
       </c>
       <c r="C90" t="s">
@@ -3137,8 +3137,8 @@
       </c>
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A91" s="14"/>
-      <c r="B91" s="15"/>
+      <c r="A91" s="11"/>
+      <c r="B91" s="7"/>
       <c r="C91" t="s">
         <v>18</v>
       </c>
@@ -3147,8 +3147,8 @@
       </c>
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A92" s="14"/>
-      <c r="B92" s="15"/>
+      <c r="A92" s="11"/>
+      <c r="B92" s="7"/>
       <c r="C92" t="s">
         <v>19</v>
       </c>
@@ -3157,8 +3157,8 @@
       </c>
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A93" s="14"/>
-      <c r="B93" s="16"/>
+      <c r="A93" s="11"/>
+      <c r="B93" s="8"/>
       <c r="C93" t="s">
         <v>20</v>
       </c>
@@ -3167,8 +3167,8 @@
       </c>
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A94" s="14"/>
-      <c r="B94" s="17" t="s">
+      <c r="A94" s="11"/>
+      <c r="B94" s="4" t="s">
         <v>13</v>
       </c>
       <c r="C94" t="s">
@@ -3179,8 +3179,8 @@
       </c>
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A95" s="14"/>
-      <c r="B95" s="15"/>
+      <c r="A95" s="11"/>
+      <c r="B95" s="7"/>
       <c r="C95" t="s">
         <v>18</v>
       </c>
@@ -3189,8 +3189,8 @@
       </c>
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A96" s="14"/>
-      <c r="B96" s="15"/>
+      <c r="A96" s="11"/>
+      <c r="B96" s="7"/>
       <c r="C96" t="s">
         <v>19</v>
       </c>
@@ -3199,8 +3199,8 @@
       </c>
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A97" s="14"/>
-      <c r="B97" s="16"/>
+      <c r="A97" s="11"/>
+      <c r="B97" s="8"/>
       <c r="C97" t="s">
         <v>20</v>
       </c>
@@ -3209,8 +3209,8 @@
       </c>
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A98" s="14"/>
-      <c r="B98" s="17" t="s">
+      <c r="A98" s="11"/>
+      <c r="B98" s="4" t="s">
         <v>14</v>
       </c>
       <c r="C98" t="s">
@@ -3221,8 +3221,8 @@
       </c>
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A99" s="14"/>
-      <c r="B99" s="15"/>
+      <c r="A99" s="11"/>
+      <c r="B99" s="7"/>
       <c r="C99" t="s">
         <v>18</v>
       </c>
@@ -3231,8 +3231,8 @@
       </c>
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A100" s="14"/>
-      <c r="B100" s="15"/>
+      <c r="A100" s="11"/>
+      <c r="B100" s="7"/>
       <c r="C100" t="s">
         <v>19</v>
       </c>
@@ -3241,8 +3241,8 @@
       </c>
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A101" s="14"/>
-      <c r="B101" s="16"/>
+      <c r="A101" s="11"/>
+      <c r="B101" s="8"/>
       <c r="C101" t="s">
         <v>20</v>
       </c>
@@ -3251,8 +3251,8 @@
       </c>
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A102" s="14"/>
-      <c r="B102" s="17" t="s">
+      <c r="A102" s="11"/>
+      <c r="B102" s="4" t="s">
         <v>15</v>
       </c>
       <c r="C102" t="s">
@@ -3263,8 +3263,8 @@
       </c>
     </row>
     <row r="103" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A103" s="14"/>
-      <c r="B103" s="15"/>
+      <c r="A103" s="11"/>
+      <c r="B103" s="7"/>
       <c r="C103" t="s">
         <v>18</v>
       </c>
@@ -3273,8 +3273,8 @@
       </c>
     </row>
     <row r="104" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A104" s="14"/>
-      <c r="B104" s="15"/>
+      <c r="A104" s="11"/>
+      <c r="B104" s="7"/>
       <c r="C104" t="s">
         <v>19</v>
       </c>
@@ -3283,8 +3283,8 @@
       </c>
     </row>
     <row r="105" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A105" s="18"/>
-      <c r="B105" s="19"/>
+      <c r="A105" s="12"/>
+      <c r="B105" s="9"/>
       <c r="C105" t="s">
         <v>20</v>
       </c>
@@ -3293,7 +3293,7 @@
       </c>
     </row>
     <row r="106" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A106" s="12" t="s">
+      <c r="A106" s="10" t="s">
         <v>8</v>
       </c>
       <c r="B106" s="13" t="s">
@@ -3307,8 +3307,8 @@
       </c>
     </row>
     <row r="107" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A107" s="14"/>
-      <c r="B107" s="15"/>
+      <c r="A107" s="11"/>
+      <c r="B107" s="7"/>
       <c r="C107" t="s">
         <v>18</v>
       </c>
@@ -3317,8 +3317,8 @@
       </c>
     </row>
     <row r="108" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A108" s="14"/>
-      <c r="B108" s="15"/>
+      <c r="A108" s="11"/>
+      <c r="B108" s="7"/>
       <c r="C108" t="s">
         <v>19</v>
       </c>
@@ -3327,8 +3327,8 @@
       </c>
     </row>
     <row r="109" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A109" s="14"/>
-      <c r="B109" s="16"/>
+      <c r="A109" s="11"/>
+      <c r="B109" s="8"/>
       <c r="C109" t="s">
         <v>20</v>
       </c>
@@ -3337,8 +3337,8 @@
       </c>
     </row>
     <row r="110" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A110" s="14"/>
-      <c r="B110" s="17" t="s">
+      <c r="A110" s="11"/>
+      <c r="B110" s="4" t="s">
         <v>9</v>
       </c>
       <c r="C110" t="s">
@@ -3349,8 +3349,8 @@
       </c>
     </row>
     <row r="111" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A111" s="14"/>
-      <c r="B111" s="15"/>
+      <c r="A111" s="11"/>
+      <c r="B111" s="7"/>
       <c r="C111" t="s">
         <v>18</v>
       </c>
@@ -3359,8 +3359,8 @@
       </c>
     </row>
     <row r="112" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A112" s="14"/>
-      <c r="B112" s="15"/>
+      <c r="A112" s="11"/>
+      <c r="B112" s="7"/>
       <c r="C112" t="s">
         <v>19</v>
       </c>
@@ -3369,8 +3369,8 @@
       </c>
     </row>
     <row r="113" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A113" s="14"/>
-      <c r="B113" s="16"/>
+      <c r="A113" s="11"/>
+      <c r="B113" s="8"/>
       <c r="C113" t="s">
         <v>20</v>
       </c>
@@ -3379,8 +3379,8 @@
       </c>
     </row>
     <row r="114" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A114" s="14"/>
-      <c r="B114" s="17" t="s">
+      <c r="A114" s="11"/>
+      <c r="B114" s="4" t="s">
         <v>10</v>
       </c>
       <c r="C114" t="s">
@@ -3391,8 +3391,8 @@
       </c>
     </row>
     <row r="115" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A115" s="14"/>
-      <c r="B115" s="15"/>
+      <c r="A115" s="11"/>
+      <c r="B115" s="7"/>
       <c r="C115" t="s">
         <v>18</v>
       </c>
@@ -3401,8 +3401,8 @@
       </c>
     </row>
     <row r="116" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A116" s="14"/>
-      <c r="B116" s="15"/>
+      <c r="A116" s="11"/>
+      <c r="B116" s="7"/>
       <c r="C116" t="s">
         <v>19</v>
       </c>
@@ -3411,8 +3411,8 @@
       </c>
     </row>
     <row r="117" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A117" s="14"/>
-      <c r="B117" s="16"/>
+      <c r="A117" s="11"/>
+      <c r="B117" s="8"/>
       <c r="C117" t="s">
         <v>20</v>
       </c>
@@ -3421,8 +3421,8 @@
       </c>
     </row>
     <row r="118" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A118" s="14"/>
-      <c r="B118" s="17" t="s">
+      <c r="A118" s="11"/>
+      <c r="B118" s="4" t="s">
         <v>11</v>
       </c>
       <c r="C118" t="s">
@@ -3433,8 +3433,8 @@
       </c>
     </row>
     <row r="119" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A119" s="14"/>
-      <c r="B119" s="15"/>
+      <c r="A119" s="11"/>
+      <c r="B119" s="7"/>
       <c r="C119" t="s">
         <v>18</v>
       </c>
@@ -3443,8 +3443,8 @@
       </c>
     </row>
     <row r="120" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A120" s="14"/>
-      <c r="B120" s="15"/>
+      <c r="A120" s="11"/>
+      <c r="B120" s="7"/>
       <c r="C120" t="s">
         <v>19</v>
       </c>
@@ -3453,8 +3453,8 @@
       </c>
     </row>
     <row r="121" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A121" s="14"/>
-      <c r="B121" s="16"/>
+      <c r="A121" s="11"/>
+      <c r="B121" s="8"/>
       <c r="C121" t="s">
         <v>20</v>
       </c>
@@ -3463,8 +3463,8 @@
       </c>
     </row>
     <row r="122" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A122" s="14"/>
-      <c r="B122" s="17" t="s">
+      <c r="A122" s="11"/>
+      <c r="B122" s="4" t="s">
         <v>12</v>
       </c>
       <c r="C122" t="s">
@@ -3475,8 +3475,8 @@
       </c>
     </row>
     <row r="123" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A123" s="14"/>
-      <c r="B123" s="15"/>
+      <c r="A123" s="11"/>
+      <c r="B123" s="7"/>
       <c r="C123" t="s">
         <v>18</v>
       </c>
@@ -3485,8 +3485,8 @@
       </c>
     </row>
     <row r="124" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A124" s="14"/>
-      <c r="B124" s="15"/>
+      <c r="A124" s="11"/>
+      <c r="B124" s="7"/>
       <c r="C124" t="s">
         <v>19</v>
       </c>
@@ -3495,8 +3495,8 @@
       </c>
     </row>
     <row r="125" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A125" s="14"/>
-      <c r="B125" s="16"/>
+      <c r="A125" s="11"/>
+      <c r="B125" s="8"/>
       <c r="C125" t="s">
         <v>20</v>
       </c>
@@ -3505,8 +3505,8 @@
       </c>
     </row>
     <row r="126" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A126" s="14"/>
-      <c r="B126" s="17" t="s">
+      <c r="A126" s="11"/>
+      <c r="B126" s="4" t="s">
         <v>13</v>
       </c>
       <c r="C126" t="s">
@@ -3517,8 +3517,8 @@
       </c>
     </row>
     <row r="127" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A127" s="14"/>
-      <c r="B127" s="15"/>
+      <c r="A127" s="11"/>
+      <c r="B127" s="7"/>
       <c r="C127" t="s">
         <v>18</v>
       </c>
@@ -3527,8 +3527,8 @@
       </c>
     </row>
     <row r="128" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A128" s="14"/>
-      <c r="B128" s="15"/>
+      <c r="A128" s="11"/>
+      <c r="B128" s="7"/>
       <c r="C128" t="s">
         <v>19</v>
       </c>
@@ -3537,8 +3537,8 @@
       </c>
     </row>
     <row r="129" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A129" s="14"/>
-      <c r="B129" s="16"/>
+      <c r="A129" s="11"/>
+      <c r="B129" s="8"/>
       <c r="C129" t="s">
         <v>20</v>
       </c>
@@ -3547,8 +3547,8 @@
       </c>
     </row>
     <row r="130" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A130" s="14"/>
-      <c r="B130" s="17" t="s">
+      <c r="A130" s="11"/>
+      <c r="B130" s="4" t="s">
         <v>14</v>
       </c>
       <c r="C130" t="s">
@@ -3559,8 +3559,8 @@
       </c>
     </row>
     <row r="131" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A131" s="14"/>
-      <c r="B131" s="20"/>
+      <c r="A131" s="11"/>
+      <c r="B131" s="5"/>
       <c r="C131" t="s">
         <v>18</v>
       </c>
@@ -3569,8 +3569,8 @@
       </c>
     </row>
     <row r="132" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A132" s="14"/>
-      <c r="B132" s="20"/>
+      <c r="A132" s="11"/>
+      <c r="B132" s="5"/>
       <c r="C132" t="s">
         <v>19</v>
       </c>
@@ -3579,8 +3579,8 @@
       </c>
     </row>
     <row r="133" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A133" s="18"/>
-      <c r="B133" s="21"/>
+      <c r="A133" s="12"/>
+      <c r="B133" s="6"/>
       <c r="C133" t="s">
         <v>20</v>
       </c>
@@ -3589,11 +3589,11 @@
       </c>
     </row>
     <row r="134" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A134" t="s">
+      <c r="A134" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="B134" t="s">
-        <v>9</v>
+      <c r="B134" s="13" t="s">
+        <v>16</v>
       </c>
       <c r="C134" t="s">
         <v>21</v>
@@ -3603,12 +3603,8 @@
       </c>
     </row>
     <row r="135" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A135" t="s">
-        <v>8</v>
-      </c>
-      <c r="B135" t="s">
-        <v>9</v>
-      </c>
+      <c r="A135" s="11"/>
+      <c r="B135" s="7"/>
       <c r="C135" t="s">
         <v>18</v>
       </c>
@@ -3617,12 +3613,8 @@
       </c>
     </row>
     <row r="136" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A136" t="s">
-        <v>8</v>
-      </c>
-      <c r="B136" t="s">
-        <v>9</v>
-      </c>
+      <c r="A136" s="11"/>
+      <c r="B136" s="7"/>
       <c r="C136" t="s">
         <v>19</v>
       </c>
@@ -3631,12 +3623,8 @@
       </c>
     </row>
     <row r="137" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A137" t="s">
-        <v>8</v>
-      </c>
-      <c r="B137" t="s">
-        <v>9</v>
-      </c>
+      <c r="A137" s="11"/>
+      <c r="B137" s="8"/>
       <c r="C137" t="s">
         <v>20</v>
       </c>
@@ -3645,11 +3633,9 @@
       </c>
     </row>
     <row r="138" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A138" t="s">
-        <v>8</v>
-      </c>
-      <c r="B138" t="s">
-        <v>10</v>
+      <c r="A138" s="11"/>
+      <c r="B138" s="4" t="s">
+        <v>9</v>
       </c>
       <c r="C138" t="s">
         <v>21</v>
@@ -3659,12 +3645,8 @@
       </c>
     </row>
     <row r="139" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A139" t="s">
-        <v>8</v>
-      </c>
-      <c r="B139" t="s">
-        <v>10</v>
-      </c>
+      <c r="A139" s="11"/>
+      <c r="B139" s="7"/>
       <c r="C139" t="s">
         <v>18</v>
       </c>
@@ -3673,12 +3655,8 @@
       </c>
     </row>
     <row r="140" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A140" t="s">
-        <v>8</v>
-      </c>
-      <c r="B140" t="s">
-        <v>10</v>
-      </c>
+      <c r="A140" s="11"/>
+      <c r="B140" s="7"/>
       <c r="C140" t="s">
         <v>19</v>
       </c>
@@ -3687,12 +3665,8 @@
       </c>
     </row>
     <row r="141" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A141" t="s">
-        <v>8</v>
-      </c>
-      <c r="B141" t="s">
-        <v>10</v>
-      </c>
+      <c r="A141" s="11"/>
+      <c r="B141" s="8"/>
       <c r="C141" t="s">
         <v>20</v>
       </c>
@@ -3701,11 +3675,9 @@
       </c>
     </row>
     <row r="142" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A142" t="s">
-        <v>8</v>
-      </c>
-      <c r="B142" t="s">
-        <v>11</v>
+      <c r="A142" s="11"/>
+      <c r="B142" s="4" t="s">
+        <v>10</v>
       </c>
       <c r="C142" t="s">
         <v>21</v>
@@ -3715,12 +3687,8 @@
       </c>
     </row>
     <row r="143" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A143" t="s">
-        <v>8</v>
-      </c>
-      <c r="B143" t="s">
-        <v>11</v>
-      </c>
+      <c r="A143" s="11"/>
+      <c r="B143" s="7"/>
       <c r="C143" t="s">
         <v>18</v>
       </c>
@@ -3729,12 +3697,8 @@
       </c>
     </row>
     <row r="144" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A144" t="s">
-        <v>8</v>
-      </c>
-      <c r="B144" t="s">
-        <v>11</v>
-      </c>
+      <c r="A144" s="11"/>
+      <c r="B144" s="7"/>
       <c r="C144" t="s">
         <v>19</v>
       </c>
@@ -3743,12 +3707,8 @@
       </c>
     </row>
     <row r="145" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A145" t="s">
-        <v>8</v>
-      </c>
-      <c r="B145" t="s">
-        <v>11</v>
-      </c>
+      <c r="A145" s="11"/>
+      <c r="B145" s="8"/>
       <c r="C145" t="s">
         <v>20</v>
       </c>
@@ -3757,11 +3717,9 @@
       </c>
     </row>
     <row r="146" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A146" t="s">
-        <v>8</v>
-      </c>
-      <c r="B146" t="s">
-        <v>12</v>
+      <c r="A146" s="11"/>
+      <c r="B146" s="4" t="s">
+        <v>11</v>
       </c>
       <c r="C146" t="s">
         <v>21</v>
@@ -3771,12 +3729,8 @@
       </c>
     </row>
     <row r="147" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A147" t="s">
-        <v>8</v>
-      </c>
-      <c r="B147" t="s">
-        <v>12</v>
-      </c>
+      <c r="A147" s="11"/>
+      <c r="B147" s="7"/>
       <c r="C147" t="s">
         <v>18</v>
       </c>
@@ -3785,12 +3739,8 @@
       </c>
     </row>
     <row r="148" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A148" t="s">
-        <v>8</v>
-      </c>
-      <c r="B148" t="s">
-        <v>12</v>
-      </c>
+      <c r="A148" s="11"/>
+      <c r="B148" s="7"/>
       <c r="C148" t="s">
         <v>19</v>
       </c>
@@ -3799,12 +3749,8 @@
       </c>
     </row>
     <row r="149" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A149" t="s">
-        <v>8</v>
-      </c>
-      <c r="B149" t="s">
-        <v>12</v>
-      </c>
+      <c r="A149" s="11"/>
+      <c r="B149" s="8"/>
       <c r="C149" t="s">
         <v>20</v>
       </c>
@@ -3813,11 +3759,9 @@
       </c>
     </row>
     <row r="150" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A150" t="s">
-        <v>8</v>
-      </c>
-      <c r="B150" t="s">
-        <v>13</v>
+      <c r="A150" s="11"/>
+      <c r="B150" s="4" t="s">
+        <v>12</v>
       </c>
       <c r="C150" t="s">
         <v>21</v>
@@ -3827,12 +3771,8 @@
       </c>
     </row>
     <row r="151" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A151" t="s">
-        <v>8</v>
-      </c>
-      <c r="B151" t="s">
-        <v>13</v>
-      </c>
+      <c r="A151" s="11"/>
+      <c r="B151" s="7"/>
       <c r="C151" t="s">
         <v>18</v>
       </c>
@@ -3841,12 +3781,8 @@
       </c>
     </row>
     <row r="152" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A152" t="s">
-        <v>8</v>
-      </c>
-      <c r="B152" t="s">
-        <v>13</v>
-      </c>
+      <c r="A152" s="11"/>
+      <c r="B152" s="7"/>
       <c r="C152" t="s">
         <v>19</v>
       </c>
@@ -3855,12 +3791,8 @@
       </c>
     </row>
     <row r="153" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A153" t="s">
-        <v>8</v>
-      </c>
-      <c r="B153" t="s">
-        <v>13</v>
-      </c>
+      <c r="A153" s="11"/>
+      <c r="B153" s="8"/>
       <c r="C153" t="s">
         <v>20</v>
       </c>
@@ -3869,11 +3801,9 @@
       </c>
     </row>
     <row r="154" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A154" t="s">
-        <v>8</v>
-      </c>
-      <c r="B154" t="s">
-        <v>14</v>
+      <c r="A154" s="11"/>
+      <c r="B154" s="4" t="s">
+        <v>13</v>
       </c>
       <c r="C154" t="s">
         <v>21</v>
@@ -3883,12 +3813,8 @@
       </c>
     </row>
     <row r="155" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A155" t="s">
-        <v>8</v>
-      </c>
-      <c r="B155" t="s">
-        <v>14</v>
-      </c>
+      <c r="A155" s="11"/>
+      <c r="B155" s="7"/>
       <c r="C155" t="s">
         <v>18</v>
       </c>
@@ -3897,12 +3823,8 @@
       </c>
     </row>
     <row r="156" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A156" t="s">
-        <v>8</v>
-      </c>
-      <c r="B156" t="s">
-        <v>14</v>
-      </c>
+      <c r="A156" s="11"/>
+      <c r="B156" s="7"/>
       <c r="C156" t="s">
         <v>19</v>
       </c>
@@ -3911,12 +3833,8 @@
       </c>
     </row>
     <row r="157" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A157" t="s">
-        <v>8</v>
-      </c>
-      <c r="B157" t="s">
-        <v>14</v>
-      </c>
+      <c r="A157" s="11"/>
+      <c r="B157" s="8"/>
       <c r="C157" t="s">
         <v>20</v>
       </c>
@@ -3925,11 +3843,9 @@
       </c>
     </row>
     <row r="158" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A158" t="s">
-        <v>8</v>
-      </c>
-      <c r="B158" t="s">
-        <v>15</v>
+      <c r="A158" s="11"/>
+      <c r="B158" s="4" t="s">
+        <v>14</v>
       </c>
       <c r="C158" t="s">
         <v>21</v>
@@ -3939,12 +3855,8 @@
       </c>
     </row>
     <row r="159" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A159" t="s">
-        <v>8</v>
-      </c>
-      <c r="B159" t="s">
-        <v>15</v>
-      </c>
+      <c r="A159" s="11"/>
+      <c r="B159" s="5"/>
       <c r="C159" t="s">
         <v>18</v>
       </c>
@@ -3953,12 +3865,8 @@
       </c>
     </row>
     <row r="160" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A160" t="s">
-        <v>8</v>
-      </c>
-      <c r="B160" t="s">
-        <v>15</v>
-      </c>
+      <c r="A160" s="11"/>
+      <c r="B160" s="5"/>
       <c r="C160" t="s">
         <v>19</v>
       </c>
@@ -3966,13 +3874,9 @@
         <v>1.306361926507059</v>
       </c>
     </row>
-    <row r="161" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A161" t="s">
-        <v>8</v>
-      </c>
-      <c r="B161" t="s">
-        <v>15</v>
-      </c>
+    <row r="161" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A161" s="12"/>
+      <c r="B161" s="6"/>
       <c r="C161" t="s">
         <v>20</v>
       </c>
@@ -3981,7 +3885,42 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="38">
+  <mergeCells count="46">
+    <mergeCell ref="A134:A161"/>
+    <mergeCell ref="B134:B137"/>
+    <mergeCell ref="B138:B141"/>
+    <mergeCell ref="B142:B145"/>
+    <mergeCell ref="B146:B149"/>
+    <mergeCell ref="B150:B153"/>
+    <mergeCell ref="B154:B157"/>
+    <mergeCell ref="B158:B161"/>
+    <mergeCell ref="A2:A29"/>
+    <mergeCell ref="B2:B5"/>
+    <mergeCell ref="B6:B9"/>
+    <mergeCell ref="B10:B13"/>
+    <mergeCell ref="B14:B17"/>
+    <mergeCell ref="B18:B21"/>
+    <mergeCell ref="B22:B25"/>
+    <mergeCell ref="B26:B29"/>
+    <mergeCell ref="A30:A61"/>
+    <mergeCell ref="B30:B33"/>
+    <mergeCell ref="B34:B37"/>
+    <mergeCell ref="B38:B41"/>
+    <mergeCell ref="B42:B45"/>
+    <mergeCell ref="B46:B49"/>
+    <mergeCell ref="B50:B53"/>
+    <mergeCell ref="B54:B57"/>
+    <mergeCell ref="B58:B61"/>
+    <mergeCell ref="A62:A73"/>
+    <mergeCell ref="B62:B65"/>
+    <mergeCell ref="B66:B69"/>
+    <mergeCell ref="B70:B73"/>
+    <mergeCell ref="A74:A105"/>
+    <mergeCell ref="B74:B77"/>
+    <mergeCell ref="B78:B81"/>
+    <mergeCell ref="B82:B85"/>
+    <mergeCell ref="B86:B89"/>
+    <mergeCell ref="B90:B93"/>
     <mergeCell ref="B130:B133"/>
     <mergeCell ref="B94:B97"/>
     <mergeCell ref="B98:B101"/>
@@ -3993,36 +3932,9 @@
     <mergeCell ref="B118:B121"/>
     <mergeCell ref="B122:B125"/>
     <mergeCell ref="B126:B129"/>
-    <mergeCell ref="A62:A73"/>
-    <mergeCell ref="B62:B65"/>
-    <mergeCell ref="B66:B69"/>
-    <mergeCell ref="B70:B73"/>
-    <mergeCell ref="A74:A105"/>
-    <mergeCell ref="B74:B77"/>
-    <mergeCell ref="B78:B81"/>
-    <mergeCell ref="B82:B85"/>
-    <mergeCell ref="B86:B89"/>
-    <mergeCell ref="B90:B93"/>
-    <mergeCell ref="A30:A61"/>
-    <mergeCell ref="B30:B33"/>
-    <mergeCell ref="B34:B37"/>
-    <mergeCell ref="B38:B41"/>
-    <mergeCell ref="B42:B45"/>
-    <mergeCell ref="B46:B49"/>
-    <mergeCell ref="B50:B53"/>
-    <mergeCell ref="B54:B57"/>
-    <mergeCell ref="B58:B61"/>
-    <mergeCell ref="A2:A29"/>
-    <mergeCell ref="B2:B5"/>
-    <mergeCell ref="B6:B9"/>
-    <mergeCell ref="B10:B13"/>
-    <mergeCell ref="B14:B17"/>
-    <mergeCell ref="B18:B21"/>
-    <mergeCell ref="B22:B25"/>
-    <mergeCell ref="B26:B29"/>
   </mergeCells>
   <conditionalFormatting sqref="D2:D161">
-    <cfRule type="cellIs" dxfId="1" priority="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="0" priority="1" operator="greaterThan">
       <formula>0.3</formula>
     </cfRule>
   </conditionalFormatting>
